--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472298</v>
       </c>
       <c r="B2" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131472381</v>
       </c>
       <c r="B3" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131472400</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131472457</v>
       </c>
       <c r="B5" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>131472489</v>
       </c>
       <c r="B6" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>131472479</v>
       </c>
       <c r="B9" t="n">
-        <v>92471</v>
+        <v>92472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131472289</v>
       </c>
       <c r="B10" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1179,52 +1179,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131472489</v>
+        <v>131472517</v>
       </c>
       <c r="B6" t="n">
-        <v>99023</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1233,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473204</v>
+        <v>473207</v>
       </c>
       <c r="R6" t="n">
-        <v>6417065</v>
+        <v>6417048</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1278,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,6 +1280,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1305,43 +1311,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131472517</v>
+        <v>131472489</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>99023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1350,13 +1365,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473207</v>
+        <v>473204</v>
       </c>
       <c r="R7" t="n">
-        <v>6417048</v>
+        <v>6417065</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1385,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1395,7 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,21 +1421,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472298</v>
       </c>
       <c r="B2" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131472381</v>
       </c>
       <c r="B3" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131472400</v>
       </c>
       <c r="B4" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131472457</v>
       </c>
       <c r="B5" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>131472489</v>
       </c>
       <c r="B7" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>131472479</v>
       </c>
       <c r="B9" t="n">
-        <v>92472</v>
+        <v>92475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131472289</v>
       </c>
       <c r="B10" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472298</v>
       </c>
       <c r="B2" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>131472381</v>
       </c>
       <c r="B3" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>131472400</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>131472457</v>
       </c>
       <c r="B5" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>131472489</v>
       </c>
       <c r="B7" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>131472479</v>
       </c>
       <c r="B9" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131472289</v>
       </c>
       <c r="B10" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -813,6 +818,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -950,6 +960,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472524</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1082,6 +1097,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472517</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1208,6 +1228,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472289</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1334,6 +1359,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1460,6 +1490,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1586,6 +1621,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472400</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1712,6 +1752,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472457</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1838,8 +1883,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131472489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>